--- a/Plant3DCatalogComposer/Resources/CatalogBuilderTemplate.xlsx
+++ b/Plant3DCatalogComposer/Resources/CatalogBuilderTemplate.xlsx
@@ -29,6 +29,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUBEND_LJ_A_BW_SCH40,FL,40" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUD_LJ_CL150," sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSK_FF_CL150,FL,150" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLLAR_LJ_A_BW_SCH40,FL,40" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLLAR_LJ_A_SH_BW_SCH40,FL,40" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1821,107 +1823,107 @@
         <t>LengthUnit</t>
       </text>
     </comment>
-    <comment ref="W2" authorId="0" shapeId="0">
+    <comment ref="AL2" authorId="0" shapeId="0">
       <text>
         <t>ShortDescription</t>
       </text>
     </comment>
-    <comment ref="X2" authorId="0" shapeId="0">
+    <comment ref="AM2" authorId="0" shapeId="0">
       <text>
         <t>CompatibleStandard</t>
       </text>
     </comment>
-    <comment ref="Y2" authorId="0" shapeId="0">
+    <comment ref="AN2" authorId="0" shapeId="0">
       <text>
         <t>DesignStd</t>
       </text>
     </comment>
-    <comment ref="Z2" authorId="0" shapeId="0">
+    <comment ref="AO2" authorId="0" shapeId="0">
       <text>
         <t>PartFamilyLongDesc</t>
       </text>
     </comment>
-    <comment ref="AA2" authorId="0" shapeId="0">
+    <comment ref="AP2" authorId="0" shapeId="0">
       <text>
         <t>PartSizeLongDesc</t>
       </text>
     </comment>
-    <comment ref="AB2" authorId="0" shapeId="0">
+    <comment ref="AQ2" authorId="0" shapeId="0">
       <text>
         <t>Material</t>
       </text>
     </comment>
-    <comment ref="AC2" authorId="0" shapeId="0">
+    <comment ref="AR2" authorId="0" shapeId="0">
       <text>
         <t>MaterialCode</t>
       </text>
     </comment>
-    <comment ref="AD2" authorId="0" shapeId="0">
+    <comment ref="AS2" authorId="0" shapeId="0">
       <text>
         <t>Weight</t>
       </text>
     </comment>
-    <comment ref="AE2" authorId="0" shapeId="0">
+    <comment ref="AT2" authorId="0" shapeId="0">
       <text>
         <t>WeightUnit</t>
       </text>
     </comment>
-    <comment ref="AH2" authorId="0" shapeId="0">
+    <comment ref="AW2" authorId="0" shapeId="0">
       <text>
         <t>PartFamilyId</t>
       </text>
     </comment>
-    <comment ref="AI2" authorId="0" shapeId="0">
+    <comment ref="AX2" authorId="0" shapeId="0">
       <text>
         <t>CatalogPartFamilyId</t>
       </text>
     </comment>
-    <comment ref="AJ2" authorId="0" shapeId="0">
+    <comment ref="AY2" authorId="0" shapeId="0">
       <text>
         <t>PartStatus</t>
       </text>
     </comment>
-    <comment ref="AK2" authorId="0" shapeId="0">
+    <comment ref="AZ2" authorId="0" shapeId="0">
       <text>
         <t>Manufacturer</t>
       </text>
     </comment>
-    <comment ref="AL2" authorId="0" shapeId="0">
+    <comment ref="BA2" authorId="0" shapeId="0">
       <text>
         <t>ItemCode</t>
       </text>
     </comment>
-    <comment ref="AM2" authorId="0" shapeId="0">
+    <comment ref="BB2" authorId="0" shapeId="0">
       <text>
         <t>DesignPressureFactor</t>
       </text>
     </comment>
-    <comment ref="AN2" authorId="0" shapeId="0">
+    <comment ref="BC2" authorId="0" shapeId="0">
       <text>
         <t>ConnectionPortCount</t>
       </text>
     </comment>
-    <comment ref="AO2" authorId="0" shapeId="0">
+    <comment ref="BD2" authorId="0" shapeId="0">
       <text>
         <t>ComponentDesignation</t>
       </text>
     </comment>
-    <comment ref="AP2" authorId="0" shapeId="0">
+    <comment ref="BE2" authorId="0" shapeId="0">
       <text>
         <t>PartCategory</t>
       </text>
     </comment>
-    <comment ref="AQ2" authorId="0" shapeId="0">
+    <comment ref="BF2" authorId="0" shapeId="0">
       <text>
         <t>ContentIsoSymbolDefinition</t>
       </text>
     </comment>
-    <comment ref="AR2" authorId="0" shapeId="0">
+    <comment ref="BG2" authorId="0" shapeId="0">
       <text>
         <t>PartVersion</t>
       </text>
     </comment>
-    <comment ref="AS2" authorId="0" shapeId="0">
+    <comment ref="BH2" authorId="0" shapeId="0">
       <text>
         <t>Status</t>
       </text>
@@ -2476,107 +2478,107 @@
         <t>LengthUnit</t>
       </text>
     </comment>
-    <comment ref="W2" authorId="0" shapeId="0">
+    <comment ref="AL2" authorId="0" shapeId="0">
       <text>
         <t>ShortDescription</t>
       </text>
     </comment>
-    <comment ref="X2" authorId="0" shapeId="0">
+    <comment ref="AM2" authorId="0" shapeId="0">
       <text>
         <t>CompatibleStandard</t>
       </text>
     </comment>
-    <comment ref="Y2" authorId="0" shapeId="0">
+    <comment ref="AN2" authorId="0" shapeId="0">
       <text>
         <t>DesignStd</t>
       </text>
     </comment>
-    <comment ref="Z2" authorId="0" shapeId="0">
+    <comment ref="AO2" authorId="0" shapeId="0">
       <text>
         <t>PartFamilyLongDesc</t>
       </text>
     </comment>
-    <comment ref="AA2" authorId="0" shapeId="0">
+    <comment ref="AP2" authorId="0" shapeId="0">
       <text>
         <t>PartSizeLongDesc</t>
       </text>
     </comment>
-    <comment ref="AB2" authorId="0" shapeId="0">
+    <comment ref="AQ2" authorId="0" shapeId="0">
       <text>
         <t>Material</t>
       </text>
     </comment>
-    <comment ref="AC2" authorId="0" shapeId="0">
+    <comment ref="AR2" authorId="0" shapeId="0">
       <text>
         <t>MaterialCode</t>
       </text>
     </comment>
-    <comment ref="AD2" authorId="0" shapeId="0">
+    <comment ref="AS2" authorId="0" shapeId="0">
       <text>
         <t>Weight</t>
       </text>
     </comment>
-    <comment ref="AE2" authorId="0" shapeId="0">
+    <comment ref="AT2" authorId="0" shapeId="0">
       <text>
         <t>WeightUnit</t>
       </text>
     </comment>
-    <comment ref="AH2" authorId="0" shapeId="0">
+    <comment ref="AW2" authorId="0" shapeId="0">
       <text>
         <t>PartFamilyId</t>
       </text>
     </comment>
-    <comment ref="AI2" authorId="0" shapeId="0">
+    <comment ref="AX2" authorId="0" shapeId="0">
       <text>
         <t>CatalogPartFamilyId</t>
       </text>
     </comment>
-    <comment ref="AJ2" authorId="0" shapeId="0">
+    <comment ref="AY2" authorId="0" shapeId="0">
       <text>
         <t>PartStatus</t>
       </text>
     </comment>
-    <comment ref="AK2" authorId="0" shapeId="0">
+    <comment ref="AZ2" authorId="0" shapeId="0">
       <text>
         <t>Manufacturer</t>
       </text>
     </comment>
-    <comment ref="AL2" authorId="0" shapeId="0">
+    <comment ref="BA2" authorId="0" shapeId="0">
       <text>
         <t>ItemCode</t>
       </text>
     </comment>
-    <comment ref="AM2" authorId="0" shapeId="0">
+    <comment ref="BB2" authorId="0" shapeId="0">
       <text>
         <t>DesignPressureFactor</t>
       </text>
     </comment>
-    <comment ref="AN2" authorId="0" shapeId="0">
+    <comment ref="BC2" authorId="0" shapeId="0">
       <text>
         <t>ConnectionPortCount</t>
       </text>
     </comment>
-    <comment ref="AO2" authorId="0" shapeId="0">
+    <comment ref="BD2" authorId="0" shapeId="0">
       <text>
         <t>ComponentDesignation</t>
       </text>
     </comment>
-    <comment ref="AP2" authorId="0" shapeId="0">
+    <comment ref="BE2" authorId="0" shapeId="0">
       <text>
         <t>PartCategory</t>
       </text>
     </comment>
-    <comment ref="AQ2" authorId="0" shapeId="0">
+    <comment ref="BF2" authorId="0" shapeId="0">
       <text>
         <t>ContentIsoSymbolDefinition</t>
       </text>
     </comment>
-    <comment ref="AR2" authorId="0" shapeId="0">
+    <comment ref="BG2" authorId="0" shapeId="0">
       <text>
         <t>PartVersion</t>
       </text>
     </comment>
-    <comment ref="AS2" authorId="0" shapeId="0">
+    <comment ref="BH2" authorId="0" shapeId="0">
       <text>
         <t>Status</t>
       </text>
@@ -11514,7 +11516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:BJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -11604,200 +11606,275 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>SizeRecordId_S-ALL</t>
+          <t>SizeRecordId_S1</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>PortName_S-ALL</t>
+          <t>PortName_S1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NominalDiameter_S-ALL</t>
+          <t>NominalDiameter_S1</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>NominalUnit_S-ALL</t>
+          <t>NominalUnit_S1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>MatchingPipeOd_S-ALL</t>
+          <t>MatchingPipeOd_S1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>EndType_S-ALL</t>
+          <t>EndType_S1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>FlangeStd_S-ALL</t>
+          <t>FlangeStd_S1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>GasketStd_S-ALL</t>
+          <t>GasketStd_S1</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Facing_S-ALL</t>
+          <t>Facing_S1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>FlangeThickness_S-ALL</t>
+          <t>FlangeThickness_S1</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>PressureClass_S-ALL</t>
+          <t>PressureClass_S1</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Schedule_S-ALL</t>
+          <t>Schedule_S1</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>WallThickness_S-ALL</t>
+          <t>WallThickness_S1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>EngagementLength_S-ALL</t>
+          <t>EngagementLength_S1</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>LengthUnit_S-ALL</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+          <t>LengthUnit_S1</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S2</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PortName_S2</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S2</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>NominalUnit_S2</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>EndType_S2</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>FlangeStd_S2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>GasketStd_S2</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S2</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>PressureClass_S2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>WallThickness_S2</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>EngagementLength_S2</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>LengthUnit_S2</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ShortDescription</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>CompatibleStandard</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>DesignStd</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PartFamilyLongDesc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>PartSizeLongDesc</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>MaterialCode</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>WeightUnit</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>SKEY</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>PartFamilyId</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>CatalogPartFamilyId</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>PartStatus</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ItemCode</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>DesignPressureFactor</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>ConnectionPortCount</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ComponentDesignation</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>PartCategory</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ContentIsoSymbolDefinition</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>PartVersion</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>PnPClassName</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ExcelFormatVersion_2.0</t>
         </is>
@@ -11841,200 +11918,275 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SizeRecordId_S-ALL</t>
+          <t>SizeRecordId_S1</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>PortName_S-ALL</t>
+          <t>PortName_S1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>NominalDiameter_S-ALL</t>
+          <t>NominalDiameter_S1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>NominalUnit_S-ALL</t>
+          <t>NominalUnit_S1</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>MatchingPipeOd_S-ALL</t>
+          <t>MatchingPipeOd_S1</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>EndType_S-ALL</t>
+          <t>EndType_S1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>FlangeStd_S-ALL</t>
+          <t>FlangeStd_S1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>GasketStd_S-ALL</t>
+          <t>GasketStd_S1</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Facing_S-ALL</t>
+          <t>Facing_S1</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>FlangeThickness_S-ALL</t>
+          <t>FlangeThickness_S1</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>PressureClass_S-ALL</t>
+          <t>PressureClass_S1</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Schedule_S-ALL</t>
+          <t>Schedule_S1</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>WallThickness_S-ALL</t>
+          <t>WallThickness_S1</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>EngagementLength_S-ALL</t>
+          <t>EngagementLength_S1</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>LengthUnit_S-ALL</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+          <t>LengthUnit_S1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PortName_S2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S2</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NominalUnit_S2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EndType_S2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>FlangeStd_S2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>GasketStd_S2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>PressureClass_S2</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>WallThickness_S2</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>EngagementLength_S2</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>LengthUnit_S2</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>ShortDescription</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>CompatibleStandard</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>DesignStd</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>PartFamilyLongDesc</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>PartSizeLongDesc</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>MaterialCode</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>WeightUnit</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>SKEY</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>PartFamilyId</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>CatalogPartFamilyId</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>PartStatus</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>ItemCode</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>DesignPressureFactor</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="BC2" s="2" t="inlineStr">
         <is>
           <t>ConnectionPortCount</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>ComponentDesignation</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>PartCategory</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>ContentIsoSymbolDefinition</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="BG2" s="2" t="inlineStr">
         <is>
           <t>PartVersion</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="BH2" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>PnPClassName</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="BJ2" s="2" t="inlineStr">
         <is>
           <t>ExcelFormatVersion_2.0</t>
         </is>
@@ -12124,41 +12276,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="AL3" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="inlineStr">
+      <c r="AO3" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA3" s="1">
+      <c r="AP3" s="1">
         <f>REPLACE(Z3, 12, 0, " DN" &amp; E3)</f>
         <v/>
       </c>
-      <c r="AB3" s="1" t="inlineStr">
+      <c r="AQ3" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12248,41 +12400,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="AL4" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="AO4" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA4" s="1">
+      <c r="AP4" s="1">
         <f>REPLACE(Z4, 12, 0, " DN" &amp; E4)</f>
         <v/>
       </c>
-      <c r="AB4" s="1" t="inlineStr">
+      <c r="AQ4" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12372,41 +12524,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W5" s="1" t="inlineStr">
+      <c r="AL5" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z5" s="1" t="inlineStr">
+      <c r="AO5" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA5" s="1">
+      <c r="AP5" s="1">
         <f>REPLACE(Z5, 12, 0, " DN" &amp; E5)</f>
         <v/>
       </c>
-      <c r="AB5" s="1" t="inlineStr">
+      <c r="AQ5" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12496,41 +12648,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W6" s="1" t="inlineStr">
+      <c r="AL6" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z6" s="1" t="inlineStr">
+      <c r="AO6" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA6" s="1">
+      <c r="AP6" s="1">
         <f>REPLACE(Z6, 12, 0, " DN" &amp; E6)</f>
         <v/>
       </c>
-      <c r="AB6" s="1" t="inlineStr">
+      <c r="AQ6" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12620,41 +12772,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="AL7" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="AO7" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA7" s="1">
+      <c r="AP7" s="1">
         <f>REPLACE(Z7, 12, 0, " DN" &amp; E7)</f>
         <v/>
       </c>
-      <c r="AB7" s="1" t="inlineStr">
+      <c r="AQ7" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12744,41 +12896,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W8" s="1" t="inlineStr">
+      <c r="AL8" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z8" s="1" t="inlineStr">
+      <c r="AO8" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA8" s="1">
+      <c r="AP8" s="1">
         <f>REPLACE(Z8, 12, 0, " DN" &amp; E8)</f>
         <v/>
       </c>
-      <c r="AB8" s="1" t="inlineStr">
+      <c r="AQ8" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12868,41 +13020,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W9" s="1" t="inlineStr">
+      <c r="AL9" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z9" s="1" t="inlineStr">
+      <c r="AO9" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA9" s="1">
+      <c r="AP9" s="1">
         <f>REPLACE(Z9, 12, 0, " DN" &amp; E9)</f>
         <v/>
       </c>
-      <c r="AB9" s="1" t="inlineStr">
+      <c r="AQ9" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -12992,41 +13144,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W10" s="1" t="inlineStr">
+      <c r="AL10" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z10" s="1" t="inlineStr">
+      <c r="AO10" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA10" s="1">
+      <c r="AP10" s="1">
         <f>REPLACE(Z10, 12, 0, " DN" &amp; E10)</f>
         <v/>
       </c>
-      <c r="AB10" s="1" t="inlineStr">
+      <c r="AQ10" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13116,41 +13268,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
+      <c r="AL11" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AO11" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA11" s="1">
+      <c r="AP11" s="1">
         <f>REPLACE(Z11, 12, 0, " DN" &amp; E11)</f>
         <v/>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AQ11" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13240,41 +13392,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W12" s="1" t="inlineStr">
+      <c r="AL12" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AO12" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA12" s="1">
+      <c r="AP12" s="1">
         <f>REPLACE(Z12, 12, 0, " DN" &amp; E12)</f>
         <v/>
       </c>
-      <c r="AB12" s="1" t="inlineStr">
+      <c r="AQ12" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13364,41 +13516,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="AL13" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AO13" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA13" s="1">
+      <c r="AP13" s="1">
         <f>REPLACE(Z13, 12, 0, " DN" &amp; E13)</f>
         <v/>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AQ13" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="BE13" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13488,41 +13640,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W14" s="1" t="inlineStr">
+      <c r="AL14" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z14" s="1" t="inlineStr">
+      <c r="AO14" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA14" s="1">
+      <c r="AP14" s="1">
         <f>REPLACE(Z14, 12, 0, " DN" &amp; E14)</f>
         <v/>
       </c>
-      <c r="AB14" s="1" t="inlineStr">
+      <c r="AQ14" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="BE14" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="BI14" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13612,41 +13764,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W15" s="1" t="inlineStr">
+      <c r="AL15" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="AO15" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA15" s="1">
+      <c r="AP15" s="1">
         <f>REPLACE(Z15, 12, 0, " DN" &amp; E15)</f>
         <v/>
       </c>
-      <c r="AB15" s="1" t="inlineStr">
+      <c r="AQ15" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="BE15" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13736,41 +13888,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
+      <c r="AL16" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z16" s="1" t="inlineStr">
+      <c r="AO16" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA16" s="1">
+      <c r="AP16" s="1">
         <f>REPLACE(Z16, 12, 0, " DN" &amp; E16)</f>
         <v/>
       </c>
-      <c r="AB16" s="1" t="inlineStr">
+      <c r="AQ16" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="BE16" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="BI16" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13860,41 +14012,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W17" s="1" t="inlineStr">
+      <c r="AL17" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z17" s="1" t="inlineStr">
+      <c r="AO17" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA17" s="1">
+      <c r="AP17" s="1">
         <f>REPLACE(Z17, 12, 0, " DN" &amp; E17)</f>
         <v/>
       </c>
-      <c r="AB17" s="1" t="inlineStr">
+      <c r="AQ17" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="BE17" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
+      <c r="BI17" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -13984,41 +14136,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W18" s="1" t="inlineStr">
+      <c r="AL18" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
+      <c r="AO18" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA18" s="1">
+      <c r="AP18" s="1">
         <f>REPLACE(Z18, 12, 0, " DN" &amp; E18)</f>
         <v/>
       </c>
-      <c r="AB18" s="1" t="inlineStr">
+      <c r="AQ18" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="BE18" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="BI18" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -14108,41 +14260,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W19" s="1" t="inlineStr">
+      <c r="AL19" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z19" s="1" t="inlineStr">
+      <c r="AO19" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA19" s="1">
+      <c r="AP19" s="1">
         <f>REPLACE(Z19, 12, 0, " DN" &amp; E19)</f>
         <v/>
       </c>
-      <c r="AB19" s="1" t="inlineStr">
+      <c r="AQ19" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="BE19" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -14232,41 +14384,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W20" s="1" t="inlineStr">
+      <c r="AL20" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z20" s="1" t="inlineStr">
+      <c r="AO20" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA20" s="1">
+      <c r="AP20" s="1">
         <f>REPLACE(Z20, 12, 0, " DN" &amp; E20)</f>
         <v/>
       </c>
-      <c r="AB20" s="1" t="inlineStr">
+      <c r="AQ20" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP20" t="inlineStr">
+      <c r="BE20" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -17548,12 +17700,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>
@@ -26381,7 +26530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:BJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -26471,200 +26620,275 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>SizeRecordId_S-ALL</t>
+          <t>SizeRecordId_S1</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>PortName_S-ALL</t>
+          <t>PortName_S1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NominalDiameter_S-ALL</t>
+          <t>NominalDiameter_S1</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>NominalUnit_S-ALL</t>
+          <t>NominalUnit_S1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>MatchingPipeOd_S-ALL</t>
+          <t>MatchingPipeOd_S1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>EndType_S-ALL</t>
+          <t>EndType_S1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>FlangeStd_S-ALL</t>
+          <t>FlangeStd_S1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>GasketStd_S-ALL</t>
+          <t>GasketStd_S1</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Facing_S-ALL</t>
+          <t>Facing_S1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>FlangeThickness_S-ALL</t>
+          <t>FlangeThickness_S1</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>PressureClass_S-ALL</t>
+          <t>PressureClass_S1</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Schedule_S-ALL</t>
+          <t>Schedule_S1</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>WallThickness_S-ALL</t>
+          <t>WallThickness_S1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>EngagementLength_S-ALL</t>
+          <t>EngagementLength_S1</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>LengthUnit_S-ALL</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+          <t>LengthUnit_S1</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S2</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PortName_S2</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S2</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>NominalUnit_S2</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>EndType_S2</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>FlangeStd_S2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>GasketStd_S2</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S2</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>PressureClass_S2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>WallThickness_S2</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>EngagementLength_S2</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>LengthUnit_S2</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ShortDescription</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>CompatibleStandard</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>DesignStd</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PartFamilyLongDesc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>PartSizeLongDesc</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>MaterialCode</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>WeightUnit</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>SKEY</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>PartFamilyId</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>CatalogPartFamilyId</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>PartStatus</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ItemCode</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>DesignPressureFactor</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>ConnectionPortCount</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ComponentDesignation</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>PartCategory</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ContentIsoSymbolDefinition</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>PartVersion</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>PnPClassName</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ExcelFormatVersion_2.0</t>
         </is>
@@ -26708,200 +26932,275 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SizeRecordId_S-ALL</t>
+          <t>SizeRecordId_S1</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>PortName_S-ALL</t>
+          <t>PortName_S1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>NominalDiameter_S-ALL</t>
+          <t>NominalDiameter_S1</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>NominalUnit_S-ALL</t>
+          <t>NominalUnit_S1</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>MatchingPipeOd_S-ALL</t>
+          <t>MatchingPipeOd_S1</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>EndType_S-ALL</t>
+          <t>EndType_S1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>FlangeStd_S-ALL</t>
+          <t>FlangeStd_S1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>GasketStd_S-ALL</t>
+          <t>GasketStd_S1</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Facing_S-ALL</t>
+          <t>Facing_S1</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>FlangeThickness_S-ALL</t>
+          <t>FlangeThickness_S1</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>PressureClass_S-ALL</t>
+          <t>PressureClass_S1</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Schedule_S-ALL</t>
+          <t>Schedule_S1</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>WallThickness_S-ALL</t>
+          <t>WallThickness_S1</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>EngagementLength_S-ALL</t>
+          <t>EngagementLength_S1</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>LengthUnit_S-ALL</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+          <t>LengthUnit_S1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PortName_S2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S2</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NominalUnit_S2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EndType_S2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>FlangeStd_S2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>GasketStd_S2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>PressureClass_S2</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>WallThickness_S2</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>EngagementLength_S2</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>LengthUnit_S2</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>ShortDescription</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>CompatibleStandard</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>DesignStd</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>PartFamilyLongDesc</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>PartSizeLongDesc</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>MaterialCode</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>WeightUnit</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>SKEY</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>PartFamilyId</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>CatalogPartFamilyId</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>PartStatus</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>Manufacturer</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>ItemCode</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>DesignPressureFactor</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="BC2" s="2" t="inlineStr">
         <is>
           <t>ConnectionPortCount</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>ComponentDesignation</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>PartCategory</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>ContentIsoSymbolDefinition</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="BG2" s="2" t="inlineStr">
         <is>
           <t>PartVersion</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="BH2" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>PnPClassName</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="BJ2" s="2" t="inlineStr">
         <is>
           <t>ExcelFormatVersion_2.0</t>
         </is>
@@ -26991,41 +27290,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="AL3" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="inlineStr">
+      <c r="AO3" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA3" s="1">
+      <c r="AP3" s="1">
         <f>REPLACE(Z3, 12, 0, " DN" &amp; E3)</f>
         <v/>
       </c>
-      <c r="AB3" s="1" t="inlineStr">
+      <c r="AQ3" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27115,41 +27414,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="AL4" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="AO4" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA4" s="1">
+      <c r="AP4" s="1">
         <f>REPLACE(Z4, 12, 0, " DN" &amp; E4)</f>
         <v/>
       </c>
-      <c r="AB4" s="1" t="inlineStr">
+      <c r="AQ4" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27239,41 +27538,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W5" s="1" t="inlineStr">
+      <c r="AL5" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z5" s="1" t="inlineStr">
+      <c r="AO5" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA5" s="1">
+      <c r="AP5" s="1">
         <f>REPLACE(Z5, 12, 0, " DN" &amp; E5)</f>
         <v/>
       </c>
-      <c r="AB5" s="1" t="inlineStr">
+      <c r="AQ5" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27363,41 +27662,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W6" s="1" t="inlineStr">
+      <c r="AL6" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z6" s="1" t="inlineStr">
+      <c r="AO6" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA6" s="1">
+      <c r="AP6" s="1">
         <f>REPLACE(Z6, 12, 0, " DN" &amp; E6)</f>
         <v/>
       </c>
-      <c r="AB6" s="1" t="inlineStr">
+      <c r="AQ6" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27487,41 +27786,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="AL7" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="AO7" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA7" s="1">
+      <c r="AP7" s="1">
         <f>REPLACE(Z7, 12, 0, " DN" &amp; E7)</f>
         <v/>
       </c>
-      <c r="AB7" s="1" t="inlineStr">
+      <c r="AQ7" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27611,41 +27910,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W8" s="1" t="inlineStr">
+      <c r="AL8" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z8" s="1" t="inlineStr">
+      <c r="AO8" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA8" s="1">
+      <c r="AP8" s="1">
         <f>REPLACE(Z8, 12, 0, " DN" &amp; E8)</f>
         <v/>
       </c>
-      <c r="AB8" s="1" t="inlineStr">
+      <c r="AQ8" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27735,41 +28034,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W9" s="1" t="inlineStr">
+      <c r="AL9" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z9" s="1" t="inlineStr">
+      <c r="AO9" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA9" s="1">
+      <c r="AP9" s="1">
         <f>REPLACE(Z9, 12, 0, " DN" &amp; E9)</f>
         <v/>
       </c>
-      <c r="AB9" s="1" t="inlineStr">
+      <c r="AQ9" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27859,41 +28158,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W10" s="1" t="inlineStr">
+      <c r="AL10" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z10" s="1" t="inlineStr">
+      <c r="AO10" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA10" s="1">
+      <c r="AP10" s="1">
         <f>REPLACE(Z10, 12, 0, " DN" &amp; E10)</f>
         <v/>
       </c>
-      <c r="AB10" s="1" t="inlineStr">
+      <c r="AQ10" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -27983,41 +28282,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
+      <c r="AL11" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AO11" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA11" s="1">
+      <c r="AP11" s="1">
         <f>REPLACE(Z11, 12, 0, " DN" &amp; E11)</f>
         <v/>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AQ11" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28107,41 +28406,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W12" s="1" t="inlineStr">
+      <c r="AL12" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AO12" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA12" s="1">
+      <c r="AP12" s="1">
         <f>REPLACE(Z12, 12, 0, " DN" &amp; E12)</f>
         <v/>
       </c>
-      <c r="AB12" s="1" t="inlineStr">
+      <c r="AQ12" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28231,41 +28530,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="AL13" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AO13" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA13" s="1">
+      <c r="AP13" s="1">
         <f>REPLACE(Z13, 12, 0, " DN" &amp; E13)</f>
         <v/>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AQ13" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="BE13" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28355,41 +28654,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W14" s="1" t="inlineStr">
+      <c r="AL14" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z14" s="1" t="inlineStr">
+      <c r="AO14" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA14" s="1">
+      <c r="AP14" s="1">
         <f>REPLACE(Z14, 12, 0, " DN" &amp; E14)</f>
         <v/>
       </c>
-      <c r="AB14" s="1" t="inlineStr">
+      <c r="AQ14" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="BE14" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="BI14" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28479,41 +28778,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W15" s="1" t="inlineStr">
+      <c r="AL15" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z15" s="1" t="inlineStr">
+      <c r="AO15" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA15" s="1">
+      <c r="AP15" s="1">
         <f>REPLACE(Z15, 12, 0, " DN" &amp; E15)</f>
         <v/>
       </c>
-      <c r="AB15" s="1" t="inlineStr">
+      <c r="AQ15" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="BE15" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28603,41 +28902,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
+      <c r="AL16" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z16" s="1" t="inlineStr">
+      <c r="AO16" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA16" s="1">
+      <c r="AP16" s="1">
         <f>REPLACE(Z16, 12, 0, " DN" &amp; E16)</f>
         <v/>
       </c>
-      <c r="AB16" s="1" t="inlineStr">
+      <c r="AQ16" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="BE16" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="BI16" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28727,41 +29026,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W17" s="1" t="inlineStr">
+      <c r="AL17" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z17" s="1" t="inlineStr">
+      <c r="AO17" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA17" s="1">
+      <c r="AP17" s="1">
         <f>REPLACE(Z17, 12, 0, " DN" &amp; E17)</f>
         <v/>
       </c>
-      <c r="AB17" s="1" t="inlineStr">
+      <c r="AQ17" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="BE17" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
+      <c r="BI17" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28851,41 +29150,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W18" s="1" t="inlineStr">
+      <c r="AL18" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
+      <c r="AO18" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA18" s="1">
+      <c r="AP18" s="1">
         <f>REPLACE(Z18, 12, 0, " DN" &amp; E18)</f>
         <v/>
       </c>
-      <c r="AB18" s="1" t="inlineStr">
+      <c r="AQ18" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="BE18" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="BI18" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -28975,41 +29274,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W19" s="1" t="inlineStr">
+      <c r="AL19" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z19" s="1" t="inlineStr">
+      <c r="AO19" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA19" s="1">
+      <c r="AP19" s="1">
         <f>REPLACE(Z19, 12, 0, " DN" &amp; E19)</f>
         <v/>
       </c>
-      <c r="AB19" s="1" t="inlineStr">
+      <c r="AQ19" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="BE19" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -29099,41 +29398,41 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="W20" s="1" t="inlineStr">
+      <c r="AL20" s="1" t="inlineStr">
         <is>
           <t>GSK_RF_CL150</t>
         </is>
       </c>
-      <c r="Z20" s="1" t="inlineStr">
+      <c r="AO20" s="1" t="inlineStr">
         <is>
           <t>Gasket CNAF Ring-Type CL150 Klingersil C4500</t>
         </is>
       </c>
-      <c r="AA20" s="1">
+      <c r="AP20" s="1">
         <f>REPLACE(Z20, 12, 0, " DN" &amp; E20)</f>
         <v/>
       </c>
-      <c r="AB20" s="1" t="inlineStr">
+      <c r="AQ20" s="1" t="inlineStr">
         <is>
           <t>CNAF</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>ce58bef9-94c8-4641-b3c9-4c8c5712efb3</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AP20" t="inlineStr">
+      <c r="BE20" t="inlineStr">
         <is>
           <t>Fasteners</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>Gasket</t>
         </is>
@@ -29142,6 +29441,1930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BP24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLLAR_LJ_A_BW_SCH40,FL,40</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ShapeName</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ScriptPath</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ContentGeometryParamDefinition</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PortName_S1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NominalUnit_S1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>EndType_S1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>FlangeStd_S1</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>GasketStd_S1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Facing_S1</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S1</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>PressureClass_S1</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Schedule_S1</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>WallThickness_S1</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>EngagementLength_S1</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>LengthUnit_S1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>PortName_S2</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>NominalUnit_S2</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S2</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>EndType_S2</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>FlangeStd_S2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>GasketStd_S2</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S2</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>PressureClass_S2</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>WallThickness_S2</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>EngagementLength_S2</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>LengthUnit_S2</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>ShortDescription</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>CompatibleStandard</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>DesignStd</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>PartFamilyLongDesc</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>PartSizeLongDesc</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>MaterialCode</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>WeightUnit</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>SKEY</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>PartFamilyId</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>CatalogPartFamilyId</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>PartStatus</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>ItemCode</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>DesignPressureFactor</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>ConnectionPortCount</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>ComponentDesignation</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>PartCategory</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>ContentIsoSymbolDefinition</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>PartVersion</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>FlangeOffset</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>PnPClassName</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>ExcelFormatVersion_2.0</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>PnPID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Preview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shape Name</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Script Path</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DN</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ContentGeometryParamDefinition</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Size Record Id_S1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Port Name_S1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Nominal Diameter_S1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Nominal Unit_S1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Matching Pipe OD_S1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>End Type_S1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Flange Std_S1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Gasket Std_S1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Facing_S1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Flange Thickness_S1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Pressure Class_S1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Schedule_S1</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Wall Thickness_S1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Engagement Length_S1</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Port Unit_S1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Size Record Id_S2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Port Name_S2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Nominal Diameter_S2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Nominal Unit_S2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Matching Pipe OD_S2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>End Type_S2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Flange Std_S2</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Gasket Std_S2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Flange Thickness_S2</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pressure Class_S2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Wall Thickness_S2</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Engagement Length_S2</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Port Unit_S2</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Short Description</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Compatible Standard</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Design Std</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Long Description (Family)</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Long Description (Size)</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Material Code</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Weight Unit</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SKEY</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Part Family Id</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>CatalogPartFamilyId</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>PartStatus</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Design Pressure Factor</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Connection Port Count</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Component Designation</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Part Category</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Content Iso Symbol Definition</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>PartVersion</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>Flange Offset</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>PnPClassName</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>ExcelFormatVersion_2.0</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>PnPID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CUST_COLLAR_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_COLLAR_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BP24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>COLLAR_LJ_A_SH_BW_SCH40,FL,40</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>ShapeName</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ScriptPath</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DN</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>ContentGeometryParamDefinition</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S1</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>PortName_S1</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S1</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>NominalUnit_S1</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S1</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>EndType_S1</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>FlangeStd_S1</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>GasketStd_S1</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>Facing_S1</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S1</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>PressureClass_S1</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>Schedule_S1</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>WallThickness_S1</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>EngagementLength_S1</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>LengthUnit_S1</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="inlineStr">
+        <is>
+          <t>SizeRecordId_S2</t>
+        </is>
+      </c>
+      <c r="AB1" s="11" t="inlineStr">
+        <is>
+          <t>PortName_S2</t>
+        </is>
+      </c>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>NominalDiameter_S2</t>
+        </is>
+      </c>
+      <c r="AD1" s="9" t="inlineStr">
+        <is>
+          <t>NominalUnit_S2</t>
+        </is>
+      </c>
+      <c r="AE1" s="9" t="inlineStr">
+        <is>
+          <t>MatchingPipeOd_S2</t>
+        </is>
+      </c>
+      <c r="AF1" s="9" t="inlineStr">
+        <is>
+          <t>EndType_S2</t>
+        </is>
+      </c>
+      <c r="AG1" s="9" t="inlineStr">
+        <is>
+          <t>FlangeStd_S2</t>
+        </is>
+      </c>
+      <c r="AH1" s="9" t="inlineStr">
+        <is>
+          <t>GasketStd_S2</t>
+        </is>
+      </c>
+      <c r="AI1" s="9" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="9" t="inlineStr">
+        <is>
+          <t>FlangeThickness_S2</t>
+        </is>
+      </c>
+      <c r="AK1" s="9" t="inlineStr">
+        <is>
+          <t>PressureClass_S2</t>
+        </is>
+      </c>
+      <c r="AL1" s="9" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AM1" s="9" t="inlineStr">
+        <is>
+          <t>WallThickness_S2</t>
+        </is>
+      </c>
+      <c r="AN1" s="9" t="inlineStr">
+        <is>
+          <t>EngagementLength_S2</t>
+        </is>
+      </c>
+      <c r="AO1" s="9" t="inlineStr">
+        <is>
+          <t>LengthUnit_S2</t>
+        </is>
+      </c>
+      <c r="AP1" s="9" t="inlineStr">
+        <is>
+          <t>ShortDescription</t>
+        </is>
+      </c>
+      <c r="AQ1" s="9" t="inlineStr">
+        <is>
+          <t>CompatibleStandard</t>
+        </is>
+      </c>
+      <c r="AR1" s="9" t="inlineStr">
+        <is>
+          <t>DesignStd</t>
+        </is>
+      </c>
+      <c r="AS1" s="9" t="inlineStr">
+        <is>
+          <t>PartFamilyLongDesc</t>
+        </is>
+      </c>
+      <c r="AT1" s="9" t="inlineStr">
+        <is>
+          <t>PartSizeLongDesc</t>
+        </is>
+      </c>
+      <c r="AU1" s="9" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="AV1" s="9" t="inlineStr">
+        <is>
+          <t>MaterialCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="9" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="AX1" s="9" t="inlineStr">
+        <is>
+          <t>WeightUnit</t>
+        </is>
+      </c>
+      <c r="AY1" s="9" t="inlineStr">
+        <is>
+          <t>SKEY</t>
+        </is>
+      </c>
+      <c r="AZ1" s="9" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="BA1" s="10" t="inlineStr">
+        <is>
+          <t>PartFamilyId</t>
+        </is>
+      </c>
+      <c r="BB1" s="10" t="inlineStr">
+        <is>
+          <t>CatalogPartFamilyId</t>
+        </is>
+      </c>
+      <c r="BC1" s="10" t="inlineStr">
+        <is>
+          <t>PartStatus</t>
+        </is>
+      </c>
+      <c r="BD1" s="9" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="BE1" s="9" t="inlineStr">
+        <is>
+          <t>ItemCode</t>
+        </is>
+      </c>
+      <c r="BF1" s="9" t="inlineStr">
+        <is>
+          <t>DesignPressureFactor</t>
+        </is>
+      </c>
+      <c r="BG1" s="10" t="inlineStr">
+        <is>
+          <t>ConnectionPortCount</t>
+        </is>
+      </c>
+      <c r="BH1" s="9" t="inlineStr">
+        <is>
+          <t>ComponentDesignation</t>
+        </is>
+      </c>
+      <c r="BI1" s="10" t="inlineStr">
+        <is>
+          <t>PartCategory</t>
+        </is>
+      </c>
+      <c r="BJ1" s="10" t="inlineStr">
+        <is>
+          <t>ContentIsoSymbolDefinition</t>
+        </is>
+      </c>
+      <c r="BK1" s="10" t="inlineStr">
+        <is>
+          <t>PartVersion</t>
+        </is>
+      </c>
+      <c r="BL1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="BM1" s="9" t="inlineStr">
+        <is>
+          <t>FlangeOffset</t>
+        </is>
+      </c>
+      <c r="BN1" s="10" t="inlineStr">
+        <is>
+          <t>PnPClassName</t>
+        </is>
+      </c>
+      <c r="BO1" s="10" t="inlineStr">
+        <is>
+          <t>ExcelFormatVersion_2.0</t>
+        </is>
+      </c>
+      <c r="BP1" s="10" t="inlineStr">
+        <is>
+          <t>PnPID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Preview</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Shape Name</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Script Path</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DN</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>ContentGeometryParamDefinition</t>
+        </is>
+      </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>Size Record Id_S1</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="inlineStr">
+        <is>
+          <t>Port Name_S1</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>Nominal Diameter_S1</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>Nominal Unit_S1</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>Matching Pipe OD_S1</t>
+        </is>
+      </c>
+      <c r="Q2" s="12" t="inlineStr">
+        <is>
+          <t>End Type_S1</t>
+        </is>
+      </c>
+      <c r="R2" s="12" t="inlineStr">
+        <is>
+          <t>Flange Std_S1</t>
+        </is>
+      </c>
+      <c r="S2" s="12" t="inlineStr">
+        <is>
+          <t>Gasket Std_S1</t>
+        </is>
+      </c>
+      <c r="T2" s="12" t="inlineStr">
+        <is>
+          <t>Facing_S1</t>
+        </is>
+      </c>
+      <c r="U2" s="12" t="inlineStr">
+        <is>
+          <t>Flange Thickness_S1</t>
+        </is>
+      </c>
+      <c r="V2" s="12" t="inlineStr">
+        <is>
+          <t>Pressure Class_S1</t>
+        </is>
+      </c>
+      <c r="W2" s="12" t="inlineStr">
+        <is>
+          <t>Schedule_S1</t>
+        </is>
+      </c>
+      <c r="X2" s="12" t="inlineStr">
+        <is>
+          <t>Wall Thickness_S1</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
+        <is>
+          <t>Engagement Length_S1</t>
+        </is>
+      </c>
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>Port Unit_S1</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>Size Record Id_S2</t>
+        </is>
+      </c>
+      <c r="AB2" s="13" t="inlineStr">
+        <is>
+          <t>Port Name_S2</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
+        <is>
+          <t>Nominal Diameter_S2</t>
+        </is>
+      </c>
+      <c r="AD2" s="12" t="inlineStr">
+        <is>
+          <t>Nominal Unit_S2</t>
+        </is>
+      </c>
+      <c r="AE2" s="12" t="inlineStr">
+        <is>
+          <t>Matching Pipe OD_S2</t>
+        </is>
+      </c>
+      <c r="AF2" s="12" t="inlineStr">
+        <is>
+          <t>End Type_S2</t>
+        </is>
+      </c>
+      <c r="AG2" s="12" t="inlineStr">
+        <is>
+          <t>Flange Std_S2</t>
+        </is>
+      </c>
+      <c r="AH2" s="12" t="inlineStr">
+        <is>
+          <t>Gasket Std_S2</t>
+        </is>
+      </c>
+      <c r="AI2" s="12" t="inlineStr">
+        <is>
+          <t>Facing_S2</t>
+        </is>
+      </c>
+      <c r="AJ2" s="12" t="inlineStr">
+        <is>
+          <t>Flange Thickness_S2</t>
+        </is>
+      </c>
+      <c r="AK2" s="12" t="inlineStr">
+        <is>
+          <t>Pressure Class_S2</t>
+        </is>
+      </c>
+      <c r="AL2" s="12" t="inlineStr">
+        <is>
+          <t>Schedule_S2</t>
+        </is>
+      </c>
+      <c r="AM2" s="12" t="inlineStr">
+        <is>
+          <t>Wall Thickness_S2</t>
+        </is>
+      </c>
+      <c r="AN2" s="12" t="inlineStr">
+        <is>
+          <t>Engagement Length_S2</t>
+        </is>
+      </c>
+      <c r="AO2" s="12" t="inlineStr">
+        <is>
+          <t>Port Unit_S2</t>
+        </is>
+      </c>
+      <c r="AP2" s="12" t="inlineStr">
+        <is>
+          <t>Short Description</t>
+        </is>
+      </c>
+      <c r="AQ2" s="12" t="inlineStr">
+        <is>
+          <t>Compatible Standard</t>
+        </is>
+      </c>
+      <c r="AR2" s="12" t="inlineStr">
+        <is>
+          <t>Design Std</t>
+        </is>
+      </c>
+      <c r="AS2" s="12" t="inlineStr">
+        <is>
+          <t>Long Description (Family)</t>
+        </is>
+      </c>
+      <c r="AT2" s="12" t="inlineStr">
+        <is>
+          <t>Long Description (Size)</t>
+        </is>
+      </c>
+      <c r="AU2" s="12" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="AV2" s="12" t="inlineStr">
+        <is>
+          <t>Material Code</t>
+        </is>
+      </c>
+      <c r="AW2" s="12" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="AX2" s="12" t="inlineStr">
+        <is>
+          <t>Weight Unit</t>
+        </is>
+      </c>
+      <c r="AY2" s="12" t="inlineStr">
+        <is>
+          <t>SKEY</t>
+        </is>
+      </c>
+      <c r="AZ2" s="12" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="BA2" s="12" t="inlineStr">
+        <is>
+          <t>Part Family Id</t>
+        </is>
+      </c>
+      <c r="BB2" s="12" t="inlineStr">
+        <is>
+          <t>CatalogPartFamilyId</t>
+        </is>
+      </c>
+      <c r="BC2" s="12" t="inlineStr">
+        <is>
+          <t>PartStatus</t>
+        </is>
+      </c>
+      <c r="BD2" s="12" t="inlineStr">
+        <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="BE2" s="12" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="BF2" s="12" t="inlineStr">
+        <is>
+          <t>Design Pressure Factor</t>
+        </is>
+      </c>
+      <c r="BG2" s="12" t="inlineStr">
+        <is>
+          <t>Connection Port Count</t>
+        </is>
+      </c>
+      <c r="BH2" s="12" t="inlineStr">
+        <is>
+          <t>Component Designation</t>
+        </is>
+      </c>
+      <c r="BI2" s="12" t="inlineStr">
+        <is>
+          <t>Part Category</t>
+        </is>
+      </c>
+      <c r="BJ2" s="12" t="inlineStr">
+        <is>
+          <t>Content Iso Symbol Definition</t>
+        </is>
+      </c>
+      <c r="BK2" s="12" t="inlineStr">
+        <is>
+          <t>PartVersion</t>
+        </is>
+      </c>
+      <c r="BL2" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="BM2" s="12" t="inlineStr">
+        <is>
+          <t>Flange Offset</t>
+        </is>
+      </c>
+      <c r="BN2" s="12" t="inlineStr">
+        <is>
+          <t>PnPClassName</t>
+        </is>
+      </c>
+      <c r="BO2" s="12" t="inlineStr">
+        <is>
+          <t>ExcelFormatVersion_2.0</t>
+        </is>
+      </c>
+      <c r="BP2" s="12" t="inlineStr">
+        <is>
+          <t>PnPID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CUST_COLLAR_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_COLLAR_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CUST_STUBEND_LJ_A_SH_BW_SCH40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C:\AutoCAD Plant 3D 2026 Content\CPak Common\CustomScripts\CUST_STUBEND_LJ_A_SH_BW_SCH40.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
